--- a/output/02_make_meta2.Rmd/metadata_count_purity.xlsx
+++ b/output/02_make_meta2.Rmd/metadata_count_purity.xlsx
@@ -1,893 +1,889 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Jennie/Desktop/WashU/Rotation_labs/Griffith Lab/Neoantigen ML project/output/02_make_meta2.Rmd/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37706111-2932-C242-8AB7-084381ECE2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="57980" yWindow="980" windowWidth="29660" windowHeight="12380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="282">
-  <si>
-    <t>patient_id</t>
-  </si>
-  <si>
-    <t>tumor_type</t>
-  </si>
-  <si>
-    <t>trial</t>
-  </si>
-  <si>
-    <t>driver_genes</t>
-  </si>
-  <si>
-    <t>itb_review_path</t>
-  </si>
-  <si>
-    <t>all_epitopes_path</t>
-  </si>
-  <si>
-    <t>class2_path</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>include_ML</t>
-  </si>
-  <si>
-    <t>external_validation</t>
-  </si>
-  <si>
-    <t>n_peptides</t>
-  </si>
-  <si>
-    <t>n_pass</t>
-  </si>
-  <si>
-    <t>n_accept</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Gene</t>
-  </si>
-  <si>
-    <t>DNA.VAF</t>
-  </si>
-  <si>
-    <t>purity_from_driver</t>
-  </si>
-  <si>
-    <t>purity</t>
-  </si>
-  <si>
-    <t>mcdb043</t>
-  </si>
-  <si>
-    <t>Colon adenocarinoma</t>
-  </si>
-  <si>
-    <t>JLF</t>
-  </si>
-  <si>
-    <t>TP53,FAT3,PRDM2</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb043/itb-review-files/JLF-100-036-mcdb043.revd.Annotated.Neoantigen_Candidates-rev4.xlsx</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb043/pvacseq-v4-test/result-median-score2/MHC_Class_I/mcdb043-tumor-exome.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb043/pvacseq-v4-test/result-median-score2/MHC_Class_II/mcdb043-tumor-exome.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>itb_review has missing columns: Best Transcript, TSL, Allele, Prob pos, Ref Match</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>TWJF-5120-02</t>
-  </si>
-  <si>
-    <t>Pancreas</t>
-  </si>
-  <si>
-    <t>Leidos/NCI</t>
-  </si>
-  <si>
-    <t>TP53,ACVR1B,ACVR2A,AKT2,APC,ATRX,BRAF,BRCA2,DAXX,ELF3,EP300,FAT1,FAT4,GNAS,HIF1A,KRAS,MAP2K4,MEN1,PREX2,RNF43,SMAD4,SND1,STK11</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-02_BGA-2103/itb-review-files/5120-02.revd.Annotated
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="283">
+  <si>
+    <t xml:space="preserve">patient_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tumor_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">driver_genes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itb_review_path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all_epitopes_path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">class2_path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">include_ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">external_validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_peptides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_accept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNA.VAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">purity_from_driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">purity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcdb043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colon adenocarinoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53,FAT3,PRDM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb043/itb-review-files/JLF-100-036-mcdb043.revd.Annotated.Neoantigen_Candidates-rev4.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb043/pvacseq-v4-test/result-median-score2/MHC_Class_I/mcdb043-tumor-exome.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb043/pvacseq-v4-test/result-median-score2/MHC_Class_II/mcdb043-tumor-exome.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itb_review has missing columns: Best Transcript, TSL, Allele, Prob pos, Ref Match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pancreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leidos/NCI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53,ACVR1B,ACVR2A,AKT2,APC,ATRX,BRAF,BRCA2,DAXX,ELF3,EP300,FAT1,FAT4,GNAS,HIF1A,KRAS,MAP2K4,MEN1,PREX2,RNF43,SMAD4,SND1,STK11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-02_BGA-2103/itb-review-files/5120-02.revd.Annotated
 .Neoantigen_Candidates-rev3.xlsx ../itb_review/TWJF-5120-02.revd.Annotated.Neoantigen_Candidates-rev3.xlsx</t>
   </si>
   <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-02_BGA-2103/pvacseq-v4-test/result-median-score/MHC_Class_I/TWJF-5120-02-5120-02_tumor_lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-02_BGA-2103/pvacseq-v4-test/result-median-score/MHC_Class_II/TWJF-5120-02-5120-02_tumor_lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>itb_review file and class2 file rows don't match</t>
-  </si>
-  <si>
-    <t>TWJF-5120-03</t>
-  </si>
-  <si>
-    <t>missing</t>
-  </si>
-  <si>
-    <t>this was a screen fail, do not include this case.</t>
-  </si>
-  <si>
-    <t>TWJF-5120-04</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-04_BGA-2104/itb-review-files/TWJF-5120-04.ITB-revd.
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-02_BGA-2103/pvacseq-v4-test/result-median-score/MHC_Class_I/TWJF-5120-02-5120-02_tumor_lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-02_BGA-2103/pvacseq-v4-test/result-median-score/MHC_Class_II/TWJF-5120-02-5120-02_tumor_lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itb_review file and class2 file rows don't match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this was a screen fail, do not include this case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-04_BGA-2104/itb-review-files/TWJF-5120-04.ITB-revd.
 Annotated.Neoantigen_Candidates.tsv</t>
   </si>
   <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-04_BGA-2104/pvacseq-v4-test/result-median-score-2/MHC_Class_I/TWJF-5120-04-5120-04_tumor_lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-04_BGA-2104/pvacseq-v4-test/result-median-score-2/MHC_Class_II/TWJF-5120-04-5120-04_tumor_lysate.all_epitopes.aggregated.tsv</t>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-04_BGA-2104/pvacseq-v4-test/result-median-score-2/MHC_Class_I/TWJF-5120-04-5120-04_tumor_lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-04_BGA-2104/pvacseq-v4-test/result-median-score-2/MHC_Class_II/TWJF-5120-04-5120-04_tumor_lysate.all_epitopes.aggregated.tsv</t>
   </si>
   <si>
     <t xml:space="preserve">has an extra column called Percentile.Fail </t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>chr18-51065548-51065549-G-A</t>
-  </si>
-  <si>
-    <t>SMAD4</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>mcdb044</t>
-  </si>
-  <si>
-    <t>Osteosarcoma</t>
-  </si>
-  <si>
-    <t>TP53,EXT1,EXT2,RECQL4,WRN</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb044/itb-review-files/mdb044.revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb044/pvacseq-v4/result-median-score-rc11/MHC_Class_I/mcdb044-tumor-exome.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb044/pvacseq-v4/result-median-score-rc11/MHC_Class_II/mcdb044-tumor-exome
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr18-51065548-51065549-G-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMAD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcdb044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osteosarcoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53,EXT1,EXT2,RECQL4,WRN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb044/itb-review-files/mdb044.revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb044/pvacseq-v4/result-median-score-rc11/MHC_Class_I/mcdb044-tumor-exome.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb044/pvacseq-v4/result-median-score-rc11/MHC_Class_II/mcdb044-tumor-exome
 .all_epitopes.aggregated.tsv</t>
   </si>
   <si>
-    <t>chr2-209694772-209694800-GGCTACTGTGTGTTCAATAAGTACACAGT-G</t>
-  </si>
-  <si>
-    <t>MAP2</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>TWJF-10146-MD017-0016</t>
-  </si>
-  <si>
-    <t>Metastatic TNBC</t>
-  </si>
-  <si>
-    <t>CTEP</t>
-  </si>
-  <si>
-    <t>BARD1,BRCA2,RB1,TP53</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MD017-0016_BGA-2106/itb-review-files/10146-0016.Revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MD017-0016_BGA-2106/pvacseq-v4/result-median-score-rc11/MHC_Class_I/TWJF-10146-MD017-0016-tumor-lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MD017-0016_BGA-2106/pvacseq-v4/result-median-score-rc11/MHC_Class_II/TWJF-10146-MD017-0016-tumor-lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>Gue Su did genomic review, got itb file from him</t>
-  </si>
-  <si>
-    <t>chr17-7673802-7673803-G-T</t>
-  </si>
-  <si>
-    <t>TP53</t>
-  </si>
-  <si>
-    <t>TWJF-5120-06</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-06_BGA-2108/itb-review-files/5120-06.revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-06_BGA-2108/pvacseq-v4/result-median-score-rc12/MHC_Class_I/TWJF-5120-06-5120-06_tumor_lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-06_BGA-2108/pvacseq-v4/result-median-score-rc12/MHC_Class_II/TWJF-5120-06-5120-06_tumor_lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr12-25245350-25245351-C-G</t>
-  </si>
-  <si>
-    <t>KRAS</t>
-  </si>
-  <si>
-    <t>TWJF-5120-07</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-07_BGA-2109/itb-review-files/5120-07.revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-07_BGA-2109/pvacseq-v4/result-median-score-rc11/MHC_Class_I/TWJF-5120-07-5120-07_tumor_lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-07_BGA-2109/pvacseq-v4/result-median-score-rc11/MHC_Class_II/TWJF-5120-07-5120-07_tumor_lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr17-7674220-7674221-G-A</t>
-  </si>
-  <si>
-    <t>TWJF-5120-05</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-05_BGA-2107/itb-review-files/5120-05-revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-05_BGA-2107/pvacseq-v4/result-median-score-rc11/MHC_Class_I/TWJF-5120-05-5120-05_tumor_lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-05_BGA-2107/pvacseq-v4/result-median-score-rc11/MHC_Class_II/TWJF-5120-05-5120-05_tumor_lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr17-7674949-7674950-A-C</t>
-  </si>
-  <si>
-    <t>7071-04</t>
-  </si>
-  <si>
-    <t>Pancreas (liver met)</t>
-  </si>
-  <si>
-    <t>Compassionate</t>
-  </si>
-  <si>
-    <t>TP53,ACVR1B,ACVR2A,AKT2,APC,ATRX,BRAF,BRCA2,DAXX,ELF3,EP300,FAT1,FAT4,GNAS,HIF1A,KRAS,MAP2K4,MEN1,PREX2,RNF43,SMAD4,SND1,STK12</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/compassionate_use/analysis/pici_case_1/7071-04/itb-review-files/Annotated.Neoantigen_Candidates-Final.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/compassionate_use/analysis/pici_case_1/7071-04/pvacseq-v4-test/result-median-score2/MHC_Class_I/7071-04-TumorDNA.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/compassionate_use/analysis/pici_case_1/7071-04/pvacseq-v4-test/result-median-score2/MHC_Class_II/7071-04-TumorDNA.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>driver_genes are Pancreas only, CancerGeneCensus doesn't have any metastesis info; Not included because "Allele" column in itb_review file</t>
-  </si>
-  <si>
-    <t>mcdb041_original</t>
-  </si>
-  <si>
-    <t>Lung adenocarcinoma</t>
-  </si>
-  <si>
-    <t>TP53,ARAF,BIRC6,EED,GPC5,RBM10</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb041/original_tumor/itb-review-files/mcdb041.revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb041/original_tumor/pvacseq-v4/result-median-score-rc11/MHC_Class_I/JLF-100-037_TUMOR_DNA.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb041/original_tumor/pvacseq-v4/result-median-score-rc11/MHC_Class_II/JLF-100-037_TUMOR_DNA.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>mcdb041_new</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb041/new_tumor/pvacseq-v4/result-median-score-rc13/MHC_Class_I/mcdb041-TumorDNA.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb041/new_tumor/pvacseq-v4/result-median-score-rc13/MHC_Class_II/mcdb041-TumorDNA.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>mcdb045</t>
-  </si>
-  <si>
-    <t>Non-Small Cell Lung Adenocarcinoma</t>
-  </si>
-  <si>
-    <t>TP53,AKT1,ALK,BAP1,BRAF,CCDC6,CD74,DDR2,DROSHA,EGFR,EML4,ERBB2,ERBB4,EZR,FGFR2,GOLPH3,HIP1,KDR,KEAP1,KIF5B,LRIG3,MAP2K1,MAP2K2,NFE2L2,NKX2-1,NRG1,PIK3CB,PTPN13,RET,ROS1,SDC4,SLC34A2,SMARCA4,SOX2,STK11,TFG,TPM3,TPR</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb045/itb-review-files/mcdb045.revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb045/pvacseq-v4/result-median-score-rc13/MHC_Class_I/mcdb045-tumor-exome.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb045/pvacseq-v4/result-median-score-rc13/MHC_Class_II/mcdb045-tumor-exome.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr19-11013107-11013108-C-T</t>
-  </si>
-  <si>
-    <t>SMARCA4</t>
-  </si>
-  <si>
-    <t>mcdb047</t>
-  </si>
-  <si>
-    <t>Synovial Sarcoma</t>
-  </si>
-  <si>
-    <t>TP53,SS18,SS18L1,SSX1,SSX2,SSX4</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb047/itb-review-files/mcdb047.revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb047/pvacseq-v4/result-median-score-rc13/MHC_Class_II/mcdb047-tumor-exome.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr20-53985297-53985298-A-T</t>
-  </si>
-  <si>
-    <t>BCAS1</t>
-  </si>
-  <si>
-    <t>TWJF-10146-MO011-0020</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0020/itb-review-files/TWJF-10146-020.ITB-revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0020/gcp_immuno/final_results/pVACseq/mhc_i/TWJF-10146-020-1812509A_tumor_lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0020/gcp_immuno/final_results/pVACseq/mhc_ii/TWJF-10146-020-1812509A_tumor_lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>Gue Su did genomic review, got itb file from him; has ALL ".Score" columns with "IC50</t>
-  </si>
-  <si>
-    <t>chr1-3775422-3775423-G-A</t>
-  </si>
-  <si>
-    <t>SMIM1</t>
-  </si>
-  <si>
-    <t>TWJF-5120-09</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-09/itb-review-files/5120-09.revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-09/pvacseq-v4/result-median-score-rc18/MHC_Class_I/TWJF-5120-09-5120-09_tumor_lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-09/pvacseq-v4/result-median-score-rc18/MHC_Class_II/TWJF-5120-09-5120-09_tumor_lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>has ALL ".Score" columns with "IC50"</t>
-  </si>
-  <si>
-    <t>chr12-25245349-25245350-C-T</t>
-  </si>
-  <si>
-    <t>TWJF-5120-11</t>
-  </si>
-  <si>
-    <t>storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-11/itb-review-files/5120-11.revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-11/pvacseq-v4/result-median-score-rc18/MHC_Class_I/TWJF-5120-11-5120-11_tumor_lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-11/pvacseq-v4/result-median-score-rc18/MHC_Class_II/TWJF-5120-11-5120-11_tumor_lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr17-7674249-7674250-C-G</t>
-  </si>
-  <si>
-    <t>TWJF-04143-002</t>
-  </si>
-  <si>
-    <t>SCLC</t>
-  </si>
-  <si>
-    <t>Ward</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/jward2/Active/Project_HRPO_202104143_Clinical_Trial/SCLC/analysis/TWJF-04143-002/itb-review-files/04143-002.Annotated.Neoantigen_Candidates-rev2-Cys.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/jward2/Active/Project_HRPO_202104143_Clinical_Trial/SCLC/analysis/TWJF-04143-002/pvacseq-with-Cys/result-median-score-with-Cys_attempt2/MHC_Class_I/TWJF-04143-002-Tumor_Lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/jward2/Active/Project_HRPO_202104143_Clinical_Trial/SCLC/analysis/TWJF-04143-002/pvacseq-with-Cys/result-median-score-with-Cys_attempt2/MHC_Class_II/TWJF-04143-002-Tumor_Lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>Exclude for now because this is a DNA vector, and its the only one. Also this one is an outlier in terms of having a huge number of candidates.</t>
-  </si>
-  <si>
-    <t>TWJF-10146-MO011-0024</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0024/itb-review-files/10146-MO011-0024.revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0024/pvacseq-v4/result-median-score-rc21/MHC_Class_I/TWJF-10146-024-024_tumor_lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0024/pvacseq-v4/result-median-score-rc21/MHC_Class_II/TWJF-10146-024-024_tumor_lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>has SOME ".Score" columns with "IC50"</t>
-  </si>
-  <si>
-    <t>chr11-93753747-93753747-C-CA</t>
-  </si>
-  <si>
-    <t>C11orf54</t>
-  </si>
-  <si>
-    <t>10146-022</t>
-  </si>
-  <si>
-    <t>This one's marked as a sample failure on the immuno tracking sheet, so we probably don't have itb review files for it.</t>
-  </si>
-  <si>
-    <t>mcdb046</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb046/itb-review-files/mcdb046.revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb046/pvacseq-v4/result-median-score-rc20/MHC_Class_I/mcdb046-tumor-exome.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb046/pvacseq-v4/result-median-score-rc20/MHC_Class_II/mcdb046-tumor-exome.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr17-7676152-7676153-CG-C</t>
-  </si>
-  <si>
-    <t>TWJF-10146-MO011-0021</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0021/itb-review-files/10146-0021.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0021/gcp_immuno/final_results/pVACseq/mhc_i/TWJF-10146-0021-Tumor_Lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0021/gcp_immuno/final_results/pVACseq/mhc_ii/TWJF-10146-0021-Tumor_Lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr1-150750066-150750067-A-T</t>
-  </si>
-  <si>
-    <t>CTSS</t>
-  </si>
-  <si>
-    <t>TWJF-10146-MO011-0026</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0026/itb-review-files/10146-0026.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0026/gcp_immuno/final_results/pVACseq/mhc_i/TWJF-10146-0026_Tumor_Lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0026/gcp_immuno/final_results/pVACseq/mhc_ii/TWJF-10146-0026_Tumor_Lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr17-7676040-7676041-CG-C</t>
-  </si>
-  <si>
-    <t>mcdb048</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb048/itb-review-files/mcdb048.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb048/gcp_immuno/final_results_v2_pr113-test/pVACseq/mhc_i/mcdb048-tumor-exome.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb048/gcp_immuno/final_results_v2_pr113-test/pVACseq/mhc_ii/mcdb048-tumor-exome.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>itb_review and class2 have different row number, but still included in ML; has SOME ".Score" columns with "IC50"</t>
-  </si>
-  <si>
-    <t>chr18-51065585-51065585-C-CA</t>
-  </si>
-  <si>
-    <t>JLF-100-042</t>
-  </si>
-  <si>
-    <t>Glioblastoma</t>
-  </si>
-  <si>
-    <t>TP53,DAXX,GOPC,HIF1A,IDH1,IDH2,LZTR1,MDM4,PDGFRA,PIK3CA,PIK3R1,PTPRD,ROS1,SALL4,STAG2,TERT</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/JLF-100-042/itb-review-files/JLF-100-042.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/JLF-100-042/gcp_immuno/final_results_v2_pr114-test/pVACseq/mhc_i/jlf-100-042-tumor-exome.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/JLF-100-042/gcp_immuno/final_results_v2_pr114-test/pVACseq/mhc_ii/jlf-100-042-tumor-exome.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr1-158256276-158256277-G-A</t>
-  </si>
-  <si>
-    <t>CD1A</t>
-  </si>
-  <si>
-    <t>TWJF-5120-13</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-13/itb-review-files/5120-13.revd.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-13/gcp_immuno/final_results/pVACseq/mhc_i/TWJF-5120-13-2_3-Tumor_Lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-13/gcp_immuno/final_results/pVACseq/mhc_ii/TWJF-5120-13-2_3-Tumor_Lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr17-7675189-7675190-C-T</t>
-  </si>
-  <si>
-    <t>TWJF-10146-MO011-0029</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0029/itb-review-files/10146-0029.Annotated.Neoantigen_Candidates.Revd.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0029/gcp_immuno/final_results/pVACseq/mhc_i/TWJF-10146-0029-0029_Tumor_Lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0029/gcp_immuno/final_results/pVACseq/mhc_ii/TWJF-10146-0029-0029_Tumor_Lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr1-114677966-114677967-G-T</t>
-  </si>
-  <si>
-    <t>AMPD1</t>
-  </si>
-  <si>
-    <t>TWJF-10146-0011</t>
-  </si>
-  <si>
-    <t>BARD1,BRCA2,RB1,TP54</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-0011_BGA-2088/itb-review-files/TWJF-10146-0011.Annotated.Neoantigen_Candidates-revd3.xlsx</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-0011_BGA-2088/pvacseq.cwl/MHC_Class_I/TWJF-10146-0011-1770343A_tumor_lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-0011_BGA-2088/pvacseq.cwl/MHC_Class_II/TWJF-10146-0011-1770343A_tumor_lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>TWJF-10146-MD017-0004</t>
-  </si>
-  <si>
-    <t>BARD1,BRCA2,RB1,TP55</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MD017-0004_BGA-2069/itb-review-files/TWJF-10146-MD017-0004_BGA-2069.Revd.Annotated.Candidates.v17.xlsx</t>
-  </si>
-  <si>
-    <t>TWJF-10146-MD017-0005</t>
-  </si>
-  <si>
-    <t>BARD1,BRCA2,RB1,TP56</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MD017-0005_BGA-2075/itb-review-files/TWJF-10146-MD017-0005-BGA-2075_annotated_neoantigen_candidates.v15.xlsx</t>
-  </si>
-  <si>
-    <t>TWJF-10146-012</t>
-  </si>
-  <si>
-    <t>BARD1,BRCA2,RB1,TP57</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-012_BGA-2091/itb-review-files/TWJF-10146-012.revd.Annotated.Neoantigen_Candidates-rev3.xlsx</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-012_BGA-2091/pvacseq.cwl/MHC_Class_I/TWJF-10146-012-1772344A_tumor_lysate.all_epitopes.tsv</t>
+    <t xml:space="preserve">chr2-209694772-209694800-GGCTACTGTGTGTTCAATAAGTACACAGT-G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-10146-MD017-0016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metastatic TNBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARD1,BRCA2,RB1,TP53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MD017-0016_BGA-2106/itb-review-files/10146-0016.Revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MD017-0016_BGA-2106/pvacseq-v4/result-median-score-rc11/MHC_Class_I/TWJF-10146-MD017-0016-tumor-lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MD017-0016_BGA-2106/pvacseq-v4/result-median-score-rc11/MHC_Class_II/TWJF-10146-MD017-0016-tumor-lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gue Su did genomic review, got itb file from him</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7673802-7673803-G-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-06_BGA-2108/itb-review-files/5120-06.revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-06_BGA-2108/pvacseq-v4/result-median-score-rc12/MHC_Class_I/TWJF-5120-06-5120-06_tumor_lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-06_BGA-2108/pvacseq-v4/result-median-score-rc12/MHC_Class_II/TWJF-5120-06-5120-06_tumor_lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr12-25245350-25245351-C-G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-07_BGA-2109/itb-review-files/5120-07.revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-07_BGA-2109/pvacseq-v4/result-median-score-rc11/MHC_Class_I/TWJF-5120-07-5120-07_tumor_lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-07_BGA-2109/pvacseq-v4/result-median-score-rc11/MHC_Class_II/TWJF-5120-07-5120-07_tumor_lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7674220-7674221-G-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-05_BGA-2107/itb-review-files/5120-05-revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-05_BGA-2107/pvacseq-v4/result-median-score-rc11/MHC_Class_I/TWJF-5120-05-5120-05_tumor_lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-05_BGA-2107/pvacseq-v4/result-median-score-rc11/MHC_Class_II/TWJF-5120-05-5120-05_tumor_lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7674949-7674950-A-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7071-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pancreas (liver met)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compassionate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53,ACVR1B,ACVR2A,AKT2,APC,ATRX,BRAF,BRCA2,DAXX,ELF3,EP300,FAT1,FAT4,GNAS,HIF1A,KRAS,MAP2K4,MEN1,PREX2,RNF43,SMAD4,SND1,STK12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/compassionate_use/analysis/pici_case_1/7071-04/itb-review-files/Annotated.Neoantigen_Candidates-Final.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/compassionate_use/analysis/pici_case_1/7071-04/pvacseq-v4-test/result-median-score2/MHC_Class_I/7071-04-TumorDNA.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/compassionate_use/analysis/pici_case_1/7071-04/pvacseq-v4-test/result-median-score2/MHC_Class_II/7071-04-TumorDNA.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">driver_genes are Pancreas only, CancerGeneCensus doesn't have any metastesis info; Not included because "Allele" column in itb_review file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcdb041_original</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lung adenocarcinoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53,ARAF,BIRC6,EED,GPC5,RBM10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb041/original_tumor/itb-review-files/mcdb041.revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb041/original_tumor/pvacseq-v4/result-median-score-rc11/MHC_Class_I/JLF-100-037_TUMOR_DNA.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb041/original_tumor/pvacseq-v4/result-median-score-rc11/MHC_Class_II/JLF-100-037_TUMOR_DNA.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcdb041_new</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb041/new_tumor/pvacseq-v4/result-median-score-rc13/MHC_Class_I/mcdb041-TumorDNA.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb041/new_tumor/pvacseq-v4/result-median-score-rc13/MHC_Class_II/mcdb041-TumorDNA.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcdb045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Small Cell Lung Adenocarcinoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53,AKT1,ALK,BAP1,BRAF,CCDC6,CD74,DDR2,DROSHA,EGFR,EML4,ERBB2,ERBB4,EZR,FGFR2,GOLPH3,HIP1,KDR,KEAP1,KIF5B,LRIG3,MAP2K1,MAP2K2,NFE2L2,NKX2-1,NRG1,PIK3CB,PTPN13,RET,ROS1,SDC4,SLC34A2,SMARCA4,SOX2,STK11,TFG,TPM3,TPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb045/itb-review-files/mcdb045.revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb045/pvacseq-v4/result-median-score-rc13/MHC_Class_I/mcdb045-tumor-exome.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb045/pvacseq-v4/result-median-score-rc13/MHC_Class_II/mcdb045-tumor-exome.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr19-11013107-11013108-C-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMARCA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcdb047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synovial Sarcoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53,SS18,SS18L1,SSX1,SSX2,SSX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb047/itb-review-files/mcdb047.revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb047/pvacseq-v4/result-median-score-rc13/MHC_Class_II/mcdb047-tumor-exome.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr20-53985297-53985298-A-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCAS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-10146-MO011-0020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0020/itb-review-files/TWJF-10146-020.ITB-revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0020/gcp_immuno/final_results/pVACseq/mhc_i/TWJF-10146-020-1812509A_tumor_lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0020/gcp_immuno/final_results/pVACseq/mhc_ii/TWJF-10146-020-1812509A_tumor_lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gue Su did genomic review, got itb file from him; has ALL ".Score" columns with "IC50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr1-3775422-3775423-G-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMIM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-09/itb-review-files/5120-09.revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-09/pvacseq-v4/result-median-score-rc18/MHC_Class_I/TWJF-5120-09-5120-09_tumor_lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-09/pvacseq-v4/result-median-score-rc18/MHC_Class_II/TWJF-5120-09-5120-09_tumor_lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has ALL ".Score" columns with "IC50"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr12-25245349-25245350-C-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-11/itb-review-files/5120-11.revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-11/pvacseq-v4/result-median-score-rc18/MHC_Class_I/TWJF-5120-11-5120-11_tumor_lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-11/pvacseq-v4/result-median-score-rc18/MHC_Class_II/TWJF-5120-11-5120-11_tumor_lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7674249-7674250-C-G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-04143-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/jward2/Active/Project_HRPO_202104143_Clinical_Trial/SCLC/analysis/TWJF-04143-002/itb-review-files/04143-002.Annotated.Neoantigen_Candidates-rev2-Cys.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/jward2/Active/Project_HRPO_202104143_Clinical_Trial/SCLC/analysis/TWJF-04143-002/pvacseq-with-Cys/result-median-score-with-Cys_attempt2/MHC_Class_I/TWJF-04143-002-Tumor_Lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/jward2/Active/Project_HRPO_202104143_Clinical_Trial/SCLC/analysis/TWJF-04143-002/pvacseq-with-Cys/result-median-score-with-Cys_attempt2/MHC_Class_II/TWJF-04143-002-Tumor_Lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exclude for now because this is a DNA vector, and its the only one. Also this one is an outlier in terms of having a huge number of candidates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-10146-MO011-0024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0024/itb-review-files/10146-MO011-0024.revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0024/pvacseq-v4/result-median-score-rc21/MHC_Class_I/TWJF-10146-024-024_tumor_lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0024/pvacseq-v4/result-median-score-rc21/MHC_Class_II/TWJF-10146-024-024_tumor_lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has SOME ".Score" columns with "IC50"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr11-93753747-93753747-C-CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11orf54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10146-022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This one's marked as a sample failure on the immuno tracking sheet, so we probably don't have itb review files for it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcdb046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb046/itb-review-files/mcdb046.revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb046/pvacseq-v4/result-median-score-rc20/MHC_Class_I/mcdb046-tumor-exome.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb046/pvacseq-v4/result-median-score-rc20/MHC_Class_II/mcdb046-tumor-exome.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7676152-7676153-CG-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-10146-MO011-0021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0021/itb-review-files/10146-0021.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0021/gcp_immuno/final_results/pVACseq/mhc_i/TWJF-10146-0021-Tumor_Lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0021/gcp_immuno/final_results/pVACseq/mhc_ii/TWJF-10146-0021-Tumor_Lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr1-150750066-150750067-A-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-10146-MO011-0026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0026/itb-review-files/10146-0026.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0026/gcp_immuno/final_results/pVACseq/mhc_i/TWJF-10146-0026_Tumor_Lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0026/gcp_immuno/final_results/pVACseq/mhc_ii/TWJF-10146-0026_Tumor_Lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7676040-7676041-CG-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcdb048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb048/itb-review-files/mcdb048.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb048/gcp_immuno/final_results_v2_pr113-test/pVACseq/mhc_i/mcdb048-tumor-exome.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/mcdb048/gcp_immuno/final_results_v2_pr113-test/pVACseq/mhc_ii/mcdb048-tumor-exome.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">itb_review and class2 have different row number, but still included in ML; has SOME ".Score" columns with "IC50"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr18-51065585-51065585-C-CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLF-100-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glioblastoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53,DAXX,GOPC,HIF1A,IDH1,IDH2,LZTR1,MDM4,PDGFRA,PIK3CA,PIK3R1,PTPRD,ROS1,SALL4,STAG2,TERT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/JLF-100-042/itb-review-files/JLF-100-042.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/JLF-100-042/gcp_immuno/final_results_v2_pr114-test/pVACseq/mhc_i/jlf-100-042-tumor-exome.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/mgriffit/Active/JLF_MCDB/cases/JLF-100-042/gcp_immuno/final_results_v2_pr114-test/pVACseq/mhc_ii/jlf-100-042-tumor-exome.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr1-158256276-158256277-G-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-13/itb-review-files/5120-13.revd.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-13/gcp_immuno/final_results/pVACseq/mhc_i/TWJF-5120-13-2_3-Tumor_Lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-13/gcp_immuno/final_results/pVACseq/mhc_ii/TWJF-5120-13-2_3-Tumor_Lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7675189-7675190-C-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-10146-MO011-0029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0029/itb-review-files/10146-0029.Annotated.Neoantigen_Candidates.Revd.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0029/gcp_immuno/final_results/pVACseq/mhc_i/TWJF-10146-0029-0029_Tumor_Lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MO011-0029/gcp_immuno/final_results/pVACseq/mhc_ii/TWJF-10146-0029-0029_Tumor_Lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr1-114677966-114677967-G-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-10146-0011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARD1,BRCA2,RB1,TP54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-0011_BGA-2088/itb-review-files/TWJF-10146-0011.Annotated.Neoantigen_Candidates-revd3.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-0011_BGA-2088/pvacseq.cwl/MHC_Class_I/TWJF-10146-0011-1770343A_tumor_lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-0011_BGA-2088/pvacseq.cwl/MHC_Class_II/TWJF-10146-0011-1770343A_tumor_lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-10146-MD017-0004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARD1,BRCA2,RB1,TP55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MD017-0004_BGA-2069/itb-review-files/TWJF-10146-MD017-0004_BGA-2069.Revd.Annotated.Candidates.v17.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-10146-MD017-0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARD1,BRCA2,RB1,TP56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-MD017-0005_BGA-2075/itb-review-files/TWJF-10146-MD017-0005-BGA-2075_annotated_neoantigen_candidates.v15.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-10146-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARD1,BRCA2,RB1,TP57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-012_BGA-2091/itb-review-files/TWJF-10146-012.revd.Annotated.Neoantigen_Candidates-rev3.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-012_BGA-2091/pvacseq.cwl/MHC_Class_I/TWJF-10146-012-1772344A_tumor_lysate.all_epitopes.tsv</t>
   </si>
   <si>
     <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/TWJF-10146-012_BGA-2091/pvacseq.cwl/MHC_Class_II/TWJF-10146-012-1772344A_tumor_lysate.all_epitopes.aggregated.tsv </t>
   </si>
   <si>
-    <t>TWJF-10146-MO011-9999_TEST</t>
-  </si>
-  <si>
-    <t>A duplicate of TWJF-10146-MO011-0029, but changed the ID name for testing purpose</t>
-  </si>
-  <si>
-    <t>TWJF-5120-15</t>
-  </si>
-  <si>
-    <t>screen fail</t>
-  </si>
-  <si>
-    <t>TWJF-5120-16</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-16/itb-review-files/5120-16.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analy
+    <t xml:space="preserve">TWJF-5120-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">screen fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-16/itb-review-files/5120-16.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analy
 sis/TWJF-5120-16/gcp_immuno/final_results/pVACseq/mhc_i/5120_16_Tumor_FF.all_epitopes.tsv</t>
   </si>
   <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analy
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analy
 sis/TWJF-5120-16/gcp_immuno/final_results/pVACseq/mhc_ii/5120_16_Tumor_FF.all_epitopes.aggregated.tsv</t>
   </si>
   <si>
-    <t>TWJF-5120-19</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-19/itb-review-files/5120-19.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pa
+    <t xml:space="preserve">TWJF-5120-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-19/itb-review-files/5120-19.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pa
 ncreas_leidos/analysis/TWJF-5120-19/gcp_immuno/final_results_v3_relaxed_var_filters/pVACseq/mhc_i/5120_1
 9_Tumor_FF.all_epitopes.tsv</t>
   </si>
   <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pa
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pa
 ncreas_leidos/analysis/TWJF-5120-19/gcp_immuno/final_results_v3_relaxed_var_filters/pVACseq/mhc_ii/5120_
 19_Tumor_FF.all_epitopes.aggregated.tsv</t>
   </si>
   <si>
-    <t>chr17-7675087-7675088-C-T</t>
-  </si>
-  <si>
-    <t>TWJF-5120-17</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-17/itb-review-files/5120-17.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos
+    <t xml:space="preserve">chr17-7675087-7675088-C-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-17/itb-review-files/5120-17.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos
 /analysis/TWJF-5120-17/gcp_immuno/final_results/pVACseq/mhc_i/5120-17-Tumor-FF.all_epitopes.tsv</t>
   </si>
   <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos
 /analysis/TWJF-5120-17/gcp_immuno/final_results/pVACseq/mhc_ii/5120-17-Tumor-FF.all_epitopes.aggregated.tsv</t>
   </si>
   <si>
-    <t>TWJF-5120-18</t>
-  </si>
-  <si>
-    <t>TP53,ACVR1B,ACVR2A,AKT2,APC,ATRX,BRAF,BRCA2,DAXX,ELF3,EP300,FAT1,FAT4,GNAS,HIF1A,KRAS,MAP2K4,MEN1,PREX2,RNF43,SMAD4,SND1,STK13</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-18/itb-review-files/5120-18.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pa
+    <t xml:space="preserve">TWJF-5120-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53,ACVR1B,ACVR2A,AKT2,APC,ATRX,BRAF,BRCA2,DAXX,ELF3,EP300,FAT1,FAT4,GNAS,HIF1A,KRAS,MAP2K4,MEN1,PREX2,RNF43,SMAD4,SND1,STK13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-18/itb-review-files/5120-18.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pa
 ncreas_leidos/analysis/TWJF-5120-18/gcp_immuno/final_results/pVACseq/mhc_i/5120_18_Tumor_FF.all_epitopes
 .tsv</t>
   </si>
   <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pa
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pa
 ncreas_leidos/analysis/TWJF-5120-18/gcp_immuno/final_results/pVACseq/mhc_ii/5120_18_Tumor_FF.all_epitope
 s.aggregated.tsv</t>
   </si>
   <si>
-    <t>5120-39</t>
-  </si>
-  <si>
-    <t>TP53,ACVR1B,ACVR2A,AKT2,APC,ATRX,BRAF,BRCA2,DAXX,ELF3,EP300,FAT1,FAT4,GNAS,HIF1A,KRAS,MAP2K4,MEN1,PREX2,RNF43,SMAD4,SND1,STK14</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-39/itb-review-files/Leidos-39.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-39/gcp_immuno/final_results/pVACseq/mhc_i/5120-39-TumorDNA.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-39/gcp_immuno/final_results/pVACseq/mhc_ii/5120-39-TumorDNA.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr12-25227341-25227342-T-C</t>
-  </si>
-  <si>
-    <t>CTEP-10146-MD017-0052</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-0052/itb-review-files/CTEP-52.Annotated.Neoantigen_Candidates.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-0052/gcp_immuno/final_results/pVACseq/mhc_i/10146_0052_Tumor_Lysate.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-0052/gcp_immuno/final_results/pVACseq/mhc_ii/10146_0052_Tumor_Lysate.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr17-7674887-7674888-T-C</t>
-  </si>
-  <si>
-    <t>G110_Region1</t>
-  </si>
-  <si>
-    <t>Johanns</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G110/gcp_immuno_region1/final_results/pVACseq/mhc_i/TumorDNA-G110_Region1.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G110/gcp_immuno_region1/final_results/pVACseq/mhc_ii/TumorDNA-G110_Region1.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>This case involved sequencing of 2 regions of a brain tumor.</t>
-  </si>
-  <si>
-    <t>chr10-87894102-87894103-T-C</t>
-  </si>
-  <si>
-    <t>PTEN</t>
-  </si>
-  <si>
-    <t>G110_Region2</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G110/gcp_immuno_region2/final_results/pVACseq/mhc_i/TumorDNA-G110_Region2.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G110/gcp_immuno_region2/final_results/pVACseq/mhc_ii/TumorDNA-G110_Region2.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>G113_Region1</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G113/gcp_immuno_region1/final_results/pVACseq/mhc_i/TumorDNA-G113_Region1.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G113/gcp_immuno_region1/final_results/pVACseq/mhc_ii/TumorDNA-G113_Region1.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr11-123939725-123939726-T-C</t>
-  </si>
-  <si>
-    <t>OR4D5</t>
-  </si>
-  <si>
-    <t>G113_Region2</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G113/gcp_immuno_region2/final_results/pVACseq/mhc_i/TumorDNA-G113_Region2.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G113/gcp_immuno_region2/final_results/pVACseq/mhc_ii/TumorDNA-G113_Region2.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>Seems to have too many marked with "Pending" after ITB review, excluded</t>
-  </si>
-  <si>
-    <t>TWJF-5120-41</t>
-  </si>
-  <si>
-    <t>/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-41/gcp_immuno/final_results/pVACseq/mhc_i/5120-41-TumorDNA.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-41/gcp_immuno/final_results/pVACseq/mhc_ii/5120-41-TumorDNA.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr17-7673775-7673776-G-A</t>
-  </si>
-  <si>
-    <t>TWJF-5120-42</t>
-  </si>
-  <si>
-    <t>/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-42/gcp_immuno/final_results/pVACseq/mhc_i/5120-42-TumorDNA.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-42/gcp_immuno/final_results/pVACseq/mhc_ii/5120-42-TumorDNA.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr17-7673805-7673806-C-A</t>
-  </si>
-  <si>
-    <t>10146-0053</t>
-  </si>
-  <si>
-    <t>/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-FL507-0053/gcp_immuno/final_results/pVACseq/mhc_i/10146-0053-TumorDNA.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-FL507-0053/gcp_immuno/final_results/pVACseq/mhc_ii/10146-0053-TumorDNA.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr6-44255310-44255311-G-C</t>
-  </si>
-  <si>
-    <t>SLC35B2</t>
-  </si>
-  <si>
-    <t>10146-0054</t>
-  </si>
-  <si>
-    <t>/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-CO070-0054/gcp_immuno/final_results/pVACseq/mhc_i/10146-0054-TumorDNA.all_epitopes.tsv</t>
-  </si>
-  <si>
-    <t>/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-CO070-0054/gcp_immuno/final_results/pVACseq/mhc_ii/10146-0054-TumorDNA.all_epitopes.aggregated.tsv</t>
-  </si>
-  <si>
-    <t>chr20-64105860-64105861-C-T</t>
-  </si>
-  <si>
-    <t>NPBWR2</t>
-  </si>
-  <si>
-    <t>04143-004</t>
-  </si>
-  <si>
-    <t>FAM135B,RB1,TP53</t>
-  </si>
-  <si>
-    <t>A Ward case was not included in the training set</t>
-  </si>
-  <si>
-    <t>chr17-41505290-41505291-C-G</t>
-  </si>
-  <si>
-    <t>KRT13</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">5120-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53,ACVR1B,ACVR2A,AKT2,APC,ATRX,BRAF,BRCA2,DAXX,ELF3,EP300,FAT1,FAT4,GNAS,HIF1A,KRAS,MAP2K4,MEN1,PREX2,RNF43,SMAD4,SND1,STK14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-39/itb-review-files/Leidos-39.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-39/gcp_immuno/final_results/pVACseq/mhc_i/5120-39-TumorDNA.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-39/gcp_immuno/final_results/pVACseq/mhc_ii/5120-39-TumorDNA.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video analysis: before prediction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr12-25227341-25227342-T-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTEP-10146-MD017-0052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-0052/itb-review-files/CTEP-52.Annotated.Neoantigen_Candidates.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-0052/gcp_immuno/final_results/pVACseq/mhc_i/10146_0052_Tumor_Lysate.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-0052/gcp_immuno/final_results/pVACseq/mhc_ii/10146_0052_Tumor_Lysate.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7674887-7674888-T-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G110_Region1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johanns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G110/gcp_immuno_region1/final_results/pVACseq/mhc_i/TumorDNA-G110_Region1.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G110/gcp_immuno_region1/final_results/pVACseq/mhc_ii/TumorDNA-G110_Region1.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This case involved sequencing of 2 regions of a brain tumor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G110_Region2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G110/gcp_immuno_region2/final_results/pVACseq/mhc_i/TumorDNA-G110_Region2.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G110/gcp_immuno_region2/final_results/pVACseq/mhc_ii/TumorDNA-G110_Region2.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G113_Region1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G113/gcp_immuno_region1/final_results/pVACseq/mhc_i/TumorDNA-G113_Region1.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G113/gcp_immuno_region1/final_results/pVACseq/mhc_ii/TumorDNA-G113_Region1.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G113_Region2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G113/gcp_immuno_region2/final_results/pVACseq/mhc_i/TumorDNA-G113_Region2.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/storage1/fs1/gpdunn/Active/Project_0001_Clinical/gc2609/gbm_antigen_dunn/vaccine_G113/gcp_immuno_region2/final_results/pVACseq/mhc_ii/TumorDNA-G113_Region2.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seems to have too many marked with "Pending" after ITB review, excluded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-41/gcp_immuno/final_results/pVACseq/mhc_i/5120-41-TumorDNA.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-41/gcp_immuno/final_results/pVACseq/mhc_ii/5120-41-TumorDNA.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7673775-7673776-G-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-5120-42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-42/gcp_immuno/final_results/pVACseq/mhc_i/5120-42-TumorDNA.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/pancreas_leidos/analysis/TWJF-5120-42/gcp_immuno/final_results/pVACseq/mhc_ii/5120-42-TumorDNA.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7673805-7673806-C-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10146-0053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-FL507-0053/gcp_immuno/final_results/pVACseq/mhc_i/10146-0053-TumorDNA.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-FL507-0053/gcp_immuno/final_results/pVACseq/mhc_ii/10146-0053-TumorDNA.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video analysis: after prediction revealed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr6-44255310-44255311-G-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC35B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10146-0054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-CO070-0054/gcp_immuno/final_results/pVACseq/mhc_i/10146-0054-TumorDNA.all_epitopes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Volumes/gillandersw/Active/Project_0001_Clinical_Trials/CTEP/analysis/10146-CO070-0054/gcp_immuno/final_results/pVACseq/mhc_ii/10146-0054-TumorDNA.all_epitopes.aggregated.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr20-64105860-64105861-C-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPBWR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04143-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAM135B,RB1,TP53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Ward case was not included in the training set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10146-0062</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Video analysis: after prediction revealed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7674946-7674947-A-G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWJF-04143-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">chr21-32794112-32794113-C-G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21orf62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10146-0061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chr17-7675075-7675076-T-C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -923,15 +919,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1213,14 +1200,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1276,7 +1260,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1307,8 +1291,16 @@
       <c r="J2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1339,8 +1331,16 @@
       <c r="J3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -1356,6 +1356,8 @@
       <c r="E4" t="s">
         <v>36</v>
       </c>
+      <c r="F4"/>
+      <c r="G4"/>
       <c r="H4" t="s">
         <v>37</v>
       </c>
@@ -1365,8 +1367,16 @@
       <c r="J4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1397,13 +1407,13 @@
       <c r="J5" t="s">
         <v>26</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>40</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>15</v>
       </c>
       <c r="N5" t="s">
@@ -1412,17 +1422,17 @@
       <c r="O5" t="s">
         <v>45</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>0.317</v>
       </c>
       <c r="Q5" t="s">
         <v>46</v>
       </c>
-      <c r="R5">
-        <v>0.63400000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R5" t="n">
+        <v>0.634</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -1444,19 +1454,20 @@
       <c r="G6" t="s">
         <v>52</v>
       </c>
+      <c r="H6"/>
       <c r="I6" t="s">
         <v>43</v>
       </c>
       <c r="J6" t="s">
         <v>26</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>38</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>12</v>
       </c>
       <c r="N6" t="s">
@@ -1465,17 +1476,17 @@
       <c r="O6" t="s">
         <v>54</v>
       </c>
-      <c r="P6">
-        <v>0.42799999999999999</v>
+      <c r="P6" t="n">
+        <v>0.428</v>
       </c>
       <c r="Q6" t="s">
         <v>55</v>
       </c>
-      <c r="R6">
-        <v>0.85599999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R6" t="n">
+        <v>0.856</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>56</v>
       </c>
@@ -1506,13 +1517,13 @@
       <c r="J7" t="s">
         <v>26</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>50</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>10</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>14</v>
       </c>
       <c r="N7" t="s">
@@ -1521,17 +1532,17 @@
       <c r="O7" t="s">
         <v>65</v>
       </c>
-      <c r="P7">
-        <v>0.39500000000000002</v>
+      <c r="P7" t="n">
+        <v>0.395</v>
       </c>
       <c r="Q7" t="s">
         <v>46</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>0.79</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -1553,19 +1564,20 @@
       <c r="G8" t="s">
         <v>69</v>
       </c>
+      <c r="H8"/>
       <c r="I8" t="s">
         <v>43</v>
       </c>
       <c r="J8" t="s">
         <v>26</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>84</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>14</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>16</v>
       </c>
       <c r="N8" t="s">
@@ -1574,17 +1586,17 @@
       <c r="O8" t="s">
         <v>71</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>0.113</v>
       </c>
       <c r="Q8" t="s">
         <v>46</v>
       </c>
-      <c r="R8">
-        <v>0.22600000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" t="n">
+        <v>0.226</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>72</v>
       </c>
@@ -1606,19 +1618,20 @@
       <c r="G9" t="s">
         <v>75</v>
       </c>
+      <c r="H9"/>
       <c r="I9" t="s">
         <v>43</v>
       </c>
       <c r="J9" t="s">
         <v>26</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>24</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>6</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>9</v>
       </c>
       <c r="N9" t="s">
@@ -1627,17 +1640,17 @@
       <c r="O9" t="s">
         <v>65</v>
       </c>
-      <c r="P9">
-        <v>0.14299999999999999</v>
+      <c r="P9" t="n">
+        <v>0.143</v>
       </c>
       <c r="Q9" t="s">
         <v>46</v>
       </c>
-      <c r="R9">
-        <v>0.28599999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" t="n">
+        <v>0.286</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>77</v>
       </c>
@@ -1668,13 +1681,13 @@
       <c r="J10" t="s">
         <v>26</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>27</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>14</v>
       </c>
       <c r="N10" t="s">
@@ -1683,17 +1696,17 @@
       <c r="O10" t="s">
         <v>65</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>0.318</v>
       </c>
       <c r="Q10" t="s">
         <v>46</v>
       </c>
-      <c r="R10">
-        <v>0.63600000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" t="n">
+        <v>0.636</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -1724,8 +1737,16 @@
       <c r="J11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>90</v>
       </c>
@@ -1747,19 +1768,20 @@
       <c r="G12" t="s">
         <v>95</v>
       </c>
+      <c r="H12"/>
       <c r="I12" t="s">
         <v>43</v>
       </c>
       <c r="J12" t="s">
         <v>26</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>15</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>6</v>
       </c>
       <c r="N12" t="s">
@@ -1768,17 +1790,17 @@
       <c r="O12" t="s">
         <v>65</v>
       </c>
-      <c r="P12">
-        <v>7.0000000000000007E-2</v>
+      <c r="P12" t="n">
+        <v>0.07</v>
       </c>
       <c r="Q12" t="s">
         <v>46</v>
       </c>
-      <c r="R12">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -1800,19 +1822,20 @@
       <c r="G13" t="s">
         <v>98</v>
       </c>
+      <c r="H13"/>
       <c r="I13" t="s">
         <v>43</v>
       </c>
       <c r="J13" t="s">
         <v>26</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>178</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>19</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>22</v>
       </c>
       <c r="N13" t="s">
@@ -1821,17 +1844,17 @@
       <c r="O13" t="s">
         <v>65</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>0.161</v>
       </c>
       <c r="Q13" t="s">
         <v>46</v>
       </c>
-      <c r="R13">
-        <v>0.32200000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" t="n">
+        <v>0.322</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>99</v>
       </c>
@@ -1853,19 +1876,20 @@
       <c r="G14" t="s">
         <v>104</v>
       </c>
+      <c r="H14"/>
       <c r="I14" t="s">
         <v>43</v>
       </c>
       <c r="J14" t="s">
         <v>26</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>99</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>9</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>16</v>
       </c>
       <c r="N14" t="s">
@@ -1874,17 +1898,17 @@
       <c r="O14" t="s">
         <v>106</v>
       </c>
-      <c r="P14">
-        <v>7.2999999999999995E-2</v>
+      <c r="P14" t="n">
+        <v>0.073</v>
       </c>
       <c r="Q14" t="s">
         <v>46</v>
       </c>
-      <c r="R14">
-        <v>0.14599999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" t="n">
+        <v>0.146</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>107</v>
       </c>
@@ -1906,19 +1930,20 @@
       <c r="G15" t="s">
         <v>111</v>
       </c>
+      <c r="H15"/>
       <c r="I15" t="s">
         <v>43</v>
       </c>
       <c r="J15" t="s">
         <v>26</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>24</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>9</v>
       </c>
       <c r="N15" t="s">
@@ -1927,17 +1952,17 @@
       <c r="O15" t="s">
         <v>113</v>
       </c>
-      <c r="P15">
-        <v>0.48499999999999999</v>
+      <c r="P15" t="n">
+        <v>0.485</v>
       </c>
       <c r="Q15" t="s">
         <v>55</v>
       </c>
-      <c r="R15">
+      <c r="R15" t="n">
         <v>0.97</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -1968,13 +1993,13 @@
       <c r="J16" t="s">
         <v>26</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>117</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>21</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>19</v>
       </c>
       <c r="N16" t="s">
@@ -1983,17 +2008,17 @@
       <c r="O16" t="s">
         <v>120</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="n">
         <v>0.49</v>
       </c>
       <c r="Q16" t="s">
         <v>55</v>
       </c>
-      <c r="R16">
+      <c r="R16" t="n">
         <v>0.98</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -2024,13 +2049,13 @@
       <c r="J17" t="s">
         <v>26</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>32</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>13</v>
       </c>
       <c r="N17" t="s">
@@ -2039,17 +2064,17 @@
       <c r="O17" t="s">
         <v>71</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="n">
         <v>0.08</v>
       </c>
       <c r="Q17" t="s">
         <v>46</v>
       </c>
-      <c r="R17">
+      <c r="R17" t="n">
         <v>0.16</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -2080,13 +2105,13 @@
       <c r="J18" t="s">
         <v>26</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>64</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>14</v>
       </c>
       <c r="N18" t="s">
@@ -2095,17 +2120,17 @@
       <c r="O18" t="s">
         <v>65</v>
       </c>
-      <c r="P18">
-        <v>0.35799999999999998</v>
+      <c r="P18" t="n">
+        <v>0.358</v>
       </c>
       <c r="Q18" t="s">
         <v>46</v>
       </c>
-      <c r="R18">
-        <v>0.71599999999999997</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R18" t="n">
+        <v>0.716</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>132</v>
       </c>
@@ -2115,6 +2140,7 @@
       <c r="C19" t="s">
         <v>134</v>
       </c>
+      <c r="D19"/>
       <c r="E19" t="s">
         <v>135</v>
       </c>
@@ -2133,8 +2159,16 @@
       <c r="J19" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>139</v>
       </c>
@@ -2165,13 +2199,13 @@
       <c r="J20" t="s">
         <v>26</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>32</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>12</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="s">
@@ -2180,17 +2214,17 @@
       <c r="O20" t="s">
         <v>145</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="n">
         <v>0.499</v>
       </c>
       <c r="Q20" t="s">
         <v>55</v>
       </c>
-      <c r="R20">
+      <c r="R20" t="n">
         <v>0.998</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21" t="s">
         <v>146</v>
       </c>
@@ -2203,6 +2237,9 @@
       <c r="D21" t="s">
         <v>59</v>
       </c>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
       <c r="H21" t="s">
         <v>147</v>
       </c>
@@ -2212,8 +2249,16 @@
       <c r="J21" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
         <v>148</v>
       </c>
@@ -2244,13 +2289,13 @@
       <c r="J22" t="s">
         <v>26</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>51</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>7</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>17</v>
       </c>
       <c r="N22" t="s">
@@ -2259,17 +2304,17 @@
       <c r="O22" t="s">
         <v>65</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="n">
         <v>0.223</v>
       </c>
       <c r="Q22" t="s">
         <v>46</v>
       </c>
-      <c r="R22">
-        <v>0.44600000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R22" t="n">
+        <v>0.446</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
         <v>153</v>
       </c>
@@ -2300,13 +2345,13 @@
       <c r="J23" t="s">
         <v>26</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>179</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>14</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>20</v>
       </c>
       <c r="N23" t="s">
@@ -2315,17 +2360,17 @@
       <c r="O23" t="s">
         <v>158</v>
       </c>
-      <c r="P23">
-        <v>0.22800000000000001</v>
+      <c r="P23" t="n">
+        <v>0.228</v>
       </c>
       <c r="Q23" t="s">
         <v>55</v>
       </c>
-      <c r="R23">
-        <v>0.45600000000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R23" t="n">
+        <v>0.456</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
         <v>159</v>
       </c>
@@ -2356,13 +2401,13 @@
       <c r="J24" t="s">
         <v>26</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>67</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>20</v>
       </c>
       <c r="N24" t="s">
@@ -2371,17 +2416,17 @@
       <c r="O24" t="s">
         <v>65</v>
       </c>
-      <c r="P24">
-        <v>0.30099999999999999</v>
+      <c r="P24" t="n">
+        <v>0.301</v>
       </c>
       <c r="Q24" t="s">
         <v>46</v>
       </c>
-      <c r="R24">
-        <v>0.60199999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R24" t="n">
+        <v>0.602</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>164</v>
       </c>
@@ -2412,13 +2457,13 @@
       <c r="J25" t="s">
         <v>26</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>46</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="s">
@@ -2427,17 +2472,17 @@
       <c r="O25" t="s">
         <v>45</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="n">
         <v>0.121</v>
       </c>
       <c r="Q25" t="s">
         <v>46</v>
       </c>
-      <c r="R25">
-        <v>0.24199999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R25" t="n">
+        <v>0.242</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
         <v>170</v>
       </c>
@@ -2468,13 +2513,13 @@
       <c r="J26" t="s">
         <v>26</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>47</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>8</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>11</v>
       </c>
       <c r="N26" t="s">
@@ -2483,17 +2528,17 @@
       <c r="O26" t="s">
         <v>177</v>
       </c>
-      <c r="P26">
-        <v>0.38900000000000001</v>
+      <c r="P26" t="n">
+        <v>0.389</v>
       </c>
       <c r="Q26" t="s">
         <v>55</v>
       </c>
-      <c r="R26">
-        <v>0.77800000000000002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R26" t="n">
+        <v>0.778</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="s">
         <v>178</v>
       </c>
@@ -2524,13 +2569,13 @@
       <c r="J27" t="s">
         <v>26</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>48</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>9</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>15</v>
       </c>
       <c r="N27" t="s">
@@ -2539,17 +2584,17 @@
       <c r="O27" t="s">
         <v>65</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="n">
         <v>0.115</v>
       </c>
       <c r="Q27" t="s">
         <v>46</v>
       </c>
-      <c r="R27">
+      <c r="R27" t="n">
         <v>0.23</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28" t="s">
         <v>183</v>
       </c>
@@ -2580,13 +2625,13 @@
       <c r="J28" t="s">
         <v>26</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>62</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>6</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>12</v>
       </c>
       <c r="N28" t="s">
@@ -2595,17 +2640,17 @@
       <c r="O28" t="s">
         <v>188</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="n">
         <v>0.47</v>
       </c>
       <c r="Q28" t="s">
         <v>55</v>
       </c>
-      <c r="R28">
+      <c r="R28" t="n">
         <v>0.94</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29" t="s">
         <v>189</v>
       </c>
@@ -2636,8 +2681,16 @@
       <c r="J29" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+    </row>
+    <row r="30">
       <c r="A30" t="s">
         <v>194</v>
       </c>
@@ -2659,14 +2712,23 @@
       <c r="G30" t="s">
         <v>36</v>
       </c>
+      <c r="H30"/>
       <c r="I30" t="s">
         <v>26</v>
       </c>
       <c r="J30" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+    </row>
+    <row r="31">
       <c r="A31" t="s">
         <v>197</v>
       </c>
@@ -2688,14 +2750,23 @@
       <c r="G31" t="s">
         <v>36</v>
       </c>
+      <c r="H31"/>
       <c r="I31" t="s">
         <v>26</v>
       </c>
       <c r="J31" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+    </row>
+    <row r="32">
       <c r="A32" t="s">
         <v>200</v>
       </c>
@@ -2726,29 +2797,31 @@
       <c r="J32" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+    </row>
+    <row r="33">
       <c r="A33" t="s">
         <v>205</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" t="s">
-        <v>184</v>
-      </c>
-      <c r="F33" t="s">
-        <v>185</v>
-      </c>
-      <c r="G33" t="s">
-        <v>186</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
       <c r="H33" t="s">
         <v>206</v>
       </c>
@@ -2756,34 +2829,18 @@
         <v>26</v>
       </c>
       <c r="J33" t="s">
-        <v>43</v>
-      </c>
-      <c r="K33">
-        <v>62</v>
-      </c>
-      <c r="L33">
-        <v>6</v>
-      </c>
-      <c r="M33">
-        <v>12</v>
-      </c>
-      <c r="N33" t="s">
-        <v>187</v>
-      </c>
-      <c r="O33" t="s">
-        <v>188</v>
-      </c>
-      <c r="P33">
-        <v>0.47</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>55</v>
-      </c>
-      <c r="R33">
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+    </row>
+    <row r="34">
       <c r="A34" t="s">
         <v>207</v>
       </c>
@@ -2796,19 +2853,50 @@
       <c r="D34" t="s">
         <v>30</v>
       </c>
-      <c r="H34" t="s">
+      <c r="E34" t="s">
         <v>208</v>
       </c>
+      <c r="F34" t="s">
+        <v>209</v>
+      </c>
+      <c r="G34" t="s">
+        <v>210</v>
+      </c>
+      <c r="H34"/>
       <c r="I34" t="s">
         <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="K34" t="n">
+        <v>32</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>126</v>
+      </c>
+      <c r="O34" t="s">
+        <v>71</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>46</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.294</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
         <v>28</v>
@@ -2820,48 +2908,49 @@
         <v>30</v>
       </c>
       <c r="E35" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F35" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G35" t="s">
-        <v>212</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="H35"/>
       <c r="I35" t="s">
         <v>26</v>
       </c>
       <c r="J35" t="s">
         <v>43</v>
       </c>
-      <c r="K35">
-        <v>32</v>
-      </c>
-      <c r="L35">
-        <v>8</v>
-      </c>
-      <c r="M35">
+      <c r="K35" t="n">
+        <v>30</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>126</v>
+        <v>215</v>
       </c>
       <c r="O35" t="s">
-        <v>71</v>
-      </c>
-      <c r="P35">
-        <v>0.14699999999999999</v>
+        <v>65</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.071</v>
       </c>
       <c r="Q35" t="s">
         <v>46</v>
       </c>
-      <c r="R35">
-        <v>0.29399999999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R35" t="n">
+        <v>0.142</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B36" t="s">
         <v>28</v>
@@ -2870,51 +2959,52 @@
         <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="E36" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F36" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G36" t="s">
-        <v>216</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="H36"/>
       <c r="I36" t="s">
         <v>26</v>
       </c>
       <c r="J36" t="s">
         <v>43</v>
       </c>
-      <c r="K36">
-        <v>30</v>
-      </c>
-      <c r="L36">
-        <v>5</v>
-      </c>
-      <c r="M36">
+      <c r="K36" t="n">
+        <v>85</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>217</v>
+        <v>126</v>
       </c>
       <c r="O36" t="s">
-        <v>65</v>
-      </c>
-      <c r="P36">
-        <v>7.0999999999999994E-2</v>
+        <v>71</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.405</v>
       </c>
       <c r="Q36" t="s">
         <v>46</v>
       </c>
-      <c r="R36">
-        <v>0.14199999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R36" t="n">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B37" t="s">
         <v>28</v>
@@ -2923,30 +3013,31 @@
         <v>29</v>
       </c>
       <c r="D37" t="s">
-        <v>85</v>
+        <v>221</v>
       </c>
       <c r="E37" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F37" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G37" t="s">
-        <v>221</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="H37"/>
       <c r="I37" t="s">
         <v>26</v>
       </c>
       <c r="J37" t="s">
         <v>43</v>
       </c>
-      <c r="K37">
-        <v>85</v>
-      </c>
-      <c r="L37">
-        <v>1</v>
-      </c>
-      <c r="M37">
+      <c r="K37" t="n">
+        <v>23</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="s">
@@ -2955,19 +3046,19 @@
       <c r="O37" t="s">
         <v>71</v>
       </c>
-      <c r="P37">
-        <v>0.40500000000000003</v>
+      <c r="P37" t="n">
+        <v>0.113</v>
       </c>
       <c r="Q37" t="s">
         <v>46</v>
       </c>
-      <c r="R37">
-        <v>0.81</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R37" t="n">
+        <v>0.226</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B38" t="s">
         <v>28</v>
@@ -2976,16 +3067,19 @@
         <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E38" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F38" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G38" t="s">
-        <v>226</v>
+        <v>229</v>
+      </c>
+      <c r="H38" t="s">
+        <v>230</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
@@ -2993,52 +3087,55 @@
       <c r="J38" t="s">
         <v>43</v>
       </c>
-      <c r="K38">
-        <v>23</v>
-      </c>
-      <c r="L38">
-        <v>3</v>
-      </c>
-      <c r="M38">
+      <c r="K38" t="n">
+        <v>35</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5</v>
+      </c>
+      <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>126</v>
+        <v>231</v>
       </c>
       <c r="O38" t="s">
         <v>71</v>
       </c>
-      <c r="P38">
-        <v>0.113</v>
+      <c r="P38" t="n">
+        <v>0.414</v>
       </c>
       <c r="Q38" t="s">
         <v>46</v>
       </c>
-      <c r="R38">
-        <v>0.22600000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R38" t="n">
+        <v>0.828</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="D39" t="s">
-        <v>228</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F39" t="s">
+        <v>234</v>
+      </c>
+      <c r="G39" t="s">
+        <v>235</v>
+      </c>
+      <c r="H39" t="s">
         <v>230</v>
-      </c>
-      <c r="G39" t="s">
-        <v>231</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
@@ -3046,138 +3143,106 @@
       <c r="J39" t="s">
         <v>43</v>
       </c>
-      <c r="K39">
-        <v>35</v>
-      </c>
-      <c r="L39">
-        <v>5</v>
-      </c>
-      <c r="M39">
+      <c r="K39" t="n">
+        <v>72</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="O39" t="s">
-        <v>71</v>
-      </c>
-      <c r="P39">
-        <v>0.41399999999999998</v>
+        <v>65</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.419</v>
       </c>
       <c r="Q39" t="s">
         <v>46</v>
       </c>
-      <c r="R39">
-        <v>0.82799999999999996</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R39" t="n">
+        <v>0.838</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>238</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
-      </c>
-      <c r="E40" t="s">
-        <v>234</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="E40"/>
       <c r="F40" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G40" t="s">
-        <v>236</v>
+        <v>240</v>
+      </c>
+      <c r="H40" t="s">
+        <v>241</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>43</v>
-      </c>
-      <c r="K40">
-        <v>72</v>
-      </c>
-      <c r="L40">
-        <v>1</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40" t="s">
-        <v>237</v>
-      </c>
-      <c r="O40" t="s">
-        <v>65</v>
-      </c>
-      <c r="P40">
-        <v>0.41899999999999998</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>46</v>
-      </c>
-      <c r="R40">
-        <v>0.83799999999999997</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
+    </row>
+    <row r="41">
       <c r="A41" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B41" t="s">
         <v>171</v>
       </c>
       <c r="C41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D41" t="s">
         <v>172</v>
       </c>
+      <c r="E41"/>
       <c r="F41" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G41" t="s">
-        <v>241</v>
-      </c>
-      <c r="H41" t="s">
-        <v>242</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="H41"/>
       <c r="I41" t="s">
         <v>26</v>
       </c>
       <c r="J41" t="s">
-        <v>43</v>
-      </c>
-      <c r="K41">
-        <v>58</v>
-      </c>
-      <c r="L41">
-        <v>4</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41" t="s">
-        <v>243</v>
-      </c>
-      <c r="O41" t="s">
-        <v>244</v>
-      </c>
-      <c r="P41">
-        <v>0.41</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>55</v>
-      </c>
-      <c r="R41">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+    </row>
+    <row r="42">
       <c r="A42" t="s">
         <v>245</v>
       </c>
@@ -3185,49 +3250,35 @@
         <v>171</v>
       </c>
       <c r="C42" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D42" t="s">
         <v>172</v>
       </c>
+      <c r="E42"/>
       <c r="F42" t="s">
         <v>246</v>
       </c>
       <c r="G42" t="s">
         <v>247</v>
       </c>
+      <c r="H42"/>
       <c r="I42" t="s">
         <v>26</v>
       </c>
       <c r="J42" t="s">
-        <v>43</v>
-      </c>
-      <c r="K42">
-        <v>48</v>
-      </c>
-      <c r="L42">
-        <v>3</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42" t="s">
-        <v>243</v>
-      </c>
-      <c r="O42" t="s">
-        <v>244</v>
-      </c>
-      <c r="P42">
-        <v>0.35</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>55</v>
-      </c>
-      <c r="R42">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="R42"/>
+    </row>
+    <row r="43">
       <c r="A43" t="s">
         <v>248</v>
       </c>
@@ -3235,80 +3286,93 @@
         <v>171</v>
       </c>
       <c r="C43" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D43" t="s">
         <v>172</v>
       </c>
+      <c r="E43"/>
       <c r="F43" t="s">
         <v>249</v>
       </c>
       <c r="G43" t="s">
         <v>250</v>
       </c>
+      <c r="H43" t="s">
+        <v>251</v>
+      </c>
       <c r="I43" t="s">
         <v>26</v>
       </c>
       <c r="J43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="R43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>252</v>
+      </c>
+      <c r="B44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44"/>
+      <c r="F44" t="s">
+        <v>253</v>
+      </c>
+      <c r="G44" t="s">
+        <v>254</v>
+      </c>
+      <c r="H44" t="s">
+        <v>230</v>
+      </c>
+      <c r="I44" t="s">
+        <v>26</v>
+      </c>
+      <c r="J44" t="s">
         <v>43</v>
       </c>
-      <c r="K43">
-        <v>33</v>
-      </c>
-      <c r="L43">
-        <v>5</v>
-      </c>
-      <c r="M43">
+      <c r="K44" t="n">
+        <v>48</v>
+      </c>
+      <c r="L44" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="s">
-        <v>251</v>
-      </c>
-      <c r="O43" t="s">
-        <v>252</v>
-      </c>
-      <c r="P43">
-        <v>0.497</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>55</v>
-      </c>
-      <c r="R43">
-        <v>0.99399999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>253</v>
-      </c>
-      <c r="B44" t="s">
-        <v>171</v>
-      </c>
-      <c r="C44" t="s">
-        <v>239</v>
-      </c>
-      <c r="D44" t="s">
-        <v>172</v>
-      </c>
-      <c r="F44" t="s">
-        <v>254</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
         <v>255</v>
       </c>
-      <c r="H44" t="s">
+      <c r="O44" t="s">
+        <v>65</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>46</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.574</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
         <v>256</v>
-      </c>
-      <c r="I44" t="s">
-        <v>26</v>
-      </c>
-      <c r="J44" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>257</v>
       </c>
       <c r="B45" t="s">
         <v>28</v>
@@ -3319,11 +3383,15 @@
       <c r="D45" t="s">
         <v>30</v>
       </c>
+      <c r="E45"/>
       <c r="F45" t="s">
+        <v>257</v>
+      </c>
+      <c r="G45" t="s">
         <v>258</v>
       </c>
-      <c r="G45" t="s">
-        <v>259</v>
+      <c r="H45" t="s">
+        <v>230</v>
       </c>
       <c r="I45" t="s">
         <v>26</v>
@@ -3331,48 +3399,52 @@
       <c r="J45" t="s">
         <v>43</v>
       </c>
-      <c r="K45">
-        <v>48</v>
-      </c>
-      <c r="L45">
+      <c r="K45" t="n">
+        <v>32</v>
+      </c>
+      <c r="L45" t="n">
+        <v>8</v>
+      </c>
+      <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
       <c r="N45" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O45" t="s">
         <v>65</v>
       </c>
-      <c r="P45">
-        <v>0.28699999999999998</v>
+      <c r="P45" t="n">
+        <v>0.306</v>
       </c>
       <c r="Q45" t="s">
         <v>46</v>
       </c>
-      <c r="R45">
-        <v>0.57399999999999995</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R45" t="n">
+        <v>0.612</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" t="s">
+        <v>260</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46"/>
+      <c r="F46" t="s">
         <v>261</v>
       </c>
-      <c r="B46" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" t="s">
-        <v>30</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>262</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>263</v>
       </c>
       <c r="I46" t="s">
@@ -3381,34 +3453,34 @@
       <c r="J46" t="s">
         <v>43</v>
       </c>
-      <c r="K46">
-        <v>32</v>
-      </c>
-      <c r="L46">
-        <v>8</v>
-      </c>
-      <c r="M46">
+      <c r="K46" t="n">
+        <v>37</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="s">
         <v>264</v>
       </c>
       <c r="O46" t="s">
-        <v>65</v>
-      </c>
-      <c r="P46">
-        <v>0.30599999999999999</v>
+        <v>265</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.472</v>
       </c>
       <c r="Q46" t="s">
-        <v>46</v>
-      </c>
-      <c r="R46">
-        <v>0.61199999999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.944</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B47" t="s">
         <v>57</v>
@@ -3419,11 +3491,15 @@
       <c r="D47" t="s">
         <v>59</v>
       </c>
+      <c r="E47"/>
       <c r="F47" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G47" t="s">
-        <v>267</v>
+        <v>268</v>
+      </c>
+      <c r="H47" t="s">
+        <v>263</v>
       </c>
       <c r="I47" t="s">
         <v>26</v>
@@ -3431,96 +3507,83 @@
       <c r="J47" t="s">
         <v>43</v>
       </c>
-      <c r="K47">
-        <v>37</v>
-      </c>
-      <c r="L47">
-        <v>3</v>
-      </c>
-      <c r="M47">
+      <c r="K47" t="n">
+        <v>34</v>
+      </c>
+      <c r="L47" t="n">
+        <v>10</v>
+      </c>
+      <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O47" t="s">
-        <v>269</v>
-      </c>
-      <c r="P47">
-        <v>0.47199999999999998</v>
+        <v>270</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.482</v>
       </c>
       <c r="Q47" t="s">
         <v>55</v>
       </c>
-      <c r="R47">
-        <v>0.94399999999999995</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R47" t="n">
+        <v>0.964</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B48" t="s">
+        <v>133</v>
+      </c>
+      <c r="C48" t="s">
+        <v>134</v>
+      </c>
+      <c r="D48" t="s">
+        <v>272</v>
+      </c>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48" t="s">
+        <v>273</v>
+      </c>
+      <c r="I48" t="s">
+        <v>26</v>
+      </c>
+      <c r="J48" t="s">
+        <v>26</v>
+      </c>
+      <c r="K48"/>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="O48"/>
+      <c r="P48"/>
+      <c r="Q48"/>
+      <c r="R48"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49" t="s">
         <v>57</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>58</v>
       </c>
-      <c r="D48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" t="s">
-        <v>271</v>
-      </c>
-      <c r="G48" t="s">
-        <v>272</v>
-      </c>
-      <c r="I48" t="s">
-        <v>26</v>
-      </c>
-      <c r="J48" t="s">
-        <v>43</v>
-      </c>
-      <c r="K48">
-        <v>34</v>
-      </c>
-      <c r="L48">
-        <v>10</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48" t="s">
-        <v>273</v>
-      </c>
-      <c r="O48" t="s">
-        <v>274</v>
-      </c>
-      <c r="P48">
-        <v>0.48199999999999998</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>55</v>
-      </c>
-      <c r="R48">
-        <v>0.96399999999999997</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="D49" t="s">
+        <v>30</v>
+      </c>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49" t="s">
         <v>275</v>
-      </c>
-      <c r="B49" t="s">
-        <v>133</v>
-      </c>
-      <c r="C49" t="s">
-        <v>134</v>
-      </c>
-      <c r="D49" t="s">
-        <v>276</v>
-      </c>
-      <c r="H49" t="s">
-        <v>277</v>
       </c>
       <c r="I49" t="s">
         <v>26</v>
@@ -3528,65 +3591,145 @@
       <c r="J49" t="s">
         <v>43</v>
       </c>
-      <c r="K49">
-        <v>158</v>
-      </c>
-      <c r="L49">
-        <v>14</v>
-      </c>
-      <c r="M49">
+      <c r="K49" t="n">
+        <v>58</v>
+      </c>
+      <c r="L49" t="n">
+        <v>6</v>
+      </c>
+      <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="s">
+        <v>276</v>
+      </c>
+      <c r="O49" t="s">
+        <v>65</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>46</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>277</v>
+      </c>
+      <c r="B50" t="s">
+        <v>133</v>
+      </c>
+      <c r="C50" t="s">
+        <v>134</v>
+      </c>
+      <c r="D50" t="s">
+        <v>272</v>
+      </c>
+      <c r="E50" t="s">
         <v>278</v>
       </c>
-      <c r="O49" t="s">
+      <c r="F50" t="s">
+        <v>278</v>
+      </c>
+      <c r="G50" t="s">
+        <v>278</v>
+      </c>
+      <c r="H50" t="s">
+        <v>273</v>
+      </c>
+      <c r="I50" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50" t="s">
+        <v>43</v>
+      </c>
+      <c r="K50" t="n">
+        <v>157</v>
+      </c>
+      <c r="L50" t="n">
+        <v>18</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="s">
         <v>279</v>
       </c>
-      <c r="P49">
+      <c r="O50" t="s">
+        <v>280</v>
+      </c>
+      <c r="P50" t="n">
         <v>0.498</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="Q50" t="s">
         <v>55</v>
       </c>
-      <c r="R49">
+      <c r="R50" t="n">
         <v>0.996</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>280</v>
-      </c>
-      <c r="B50" t="s">
-        <v>280</v>
-      </c>
-      <c r="C50" t="s">
-        <v>280</v>
-      </c>
-      <c r="D50" t="s">
-        <v>280</v>
-      </c>
-      <c r="E50" t="s">
-        <v>280</v>
-      </c>
-      <c r="F50" t="s">
-        <v>280</v>
-      </c>
-      <c r="G50" t="s">
-        <v>280</v>
-      </c>
-      <c r="H50" t="s">
+    <row r="51">
+      <c r="A51" t="s">
         <v>281</v>
       </c>
-      <c r="I50" t="s">
-        <v>280</v>
-      </c>
-      <c r="J50" t="s">
-        <v>280</v>
+      <c r="B51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" t="s">
+        <v>278</v>
+      </c>
+      <c r="F51" t="s">
+        <v>278</v>
+      </c>
+      <c r="G51" t="s">
+        <v>278</v>
+      </c>
+      <c r="H51" t="s">
+        <v>278</v>
+      </c>
+      <c r="I51" t="s">
+        <v>26</v>
+      </c>
+      <c r="J51" t="s">
+        <v>43</v>
+      </c>
+      <c r="K51" t="n">
+        <v>221</v>
+      </c>
+      <c r="L51" t="n">
+        <v>50</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>282</v>
+      </c>
+      <c r="O51" t="s">
+        <v>65</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>46</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.968</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>